--- a/Packet Tracer/VLSM.xlsx
+++ b/Packet Tracer/VLSM.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jankok\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Vizsgaremek\Packet Tracer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C231564-2840-4D4C-BF76-C64EB74FC57C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B11DA2A-3251-4C28-A82E-89AEF109565E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2895" yWindow="2895" windowWidth="21600" windowHeight="11295" xr2:uid="{282A7FAF-A36E-4327-A1FC-20DFE78AAB8B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{282A7FAF-A36E-4327-A1FC-20DFE78AAB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="130">
   <si>
     <t>Eszköz / Interfész</t>
   </si>
@@ -66,9 +66,6 @@
     <t>255.255.255.0</t>
   </si>
   <si>
-    <t>255.255.255.1</t>
-  </si>
-  <si>
     <t>—</t>
   </si>
   <si>
@@ -78,82 +75,34 @@
     <t>ASA outside (Router felé)</t>
   </si>
   <si>
-    <t>255.255.255.2</t>
-  </si>
-  <si>
     <t>Router LAN felé néz</t>
   </si>
   <si>
     <t>Servers Router G0/0</t>
   </si>
   <si>
-    <t>255.255.255.3</t>
-  </si>
-  <si>
     <t>ASA outside szomszéd</t>
   </si>
   <si>
     <t>Servers Router G0/1 (WAN)</t>
   </si>
   <si>
-    <t>255.255.255.4</t>
-  </si>
-  <si>
     <t>WAN switch felé</t>
   </si>
   <si>
-    <t>Server0</t>
-  </si>
-  <si>
-    <t>192.168.30.10</t>
-  </si>
-  <si>
-    <t>255.255.255.5</t>
-  </si>
-  <si>
-    <t>ASA inside a gateway</t>
-  </si>
-  <si>
-    <t>Server1</t>
-  </si>
-  <si>
     <t>192.168.30.11</t>
   </si>
   <si>
-    <t>255.255.255.6</t>
-  </si>
-  <si>
-    <t>Server2</t>
-  </si>
-  <si>
     <t>192.168.30.12</t>
   </si>
   <si>
-    <t>255.255.255.7</t>
-  </si>
-  <si>
-    <t>Server3</t>
-  </si>
-  <si>
     <t>192.168.30.13</t>
   </si>
   <si>
-    <t>255.255.255.8</t>
-  </si>
-  <si>
-    <t>Server4</t>
-  </si>
-  <si>
     <t>192.168.30.14</t>
   </si>
   <si>
-    <t>255.255.255.9</t>
-  </si>
-  <si>
     <t>Switch Mgmt VLAN 99</t>
-  </si>
-  <si>
-    <t>255.255.255.10</t>
   </si>
   <si>
     <t>192.168.99.1</t>
@@ -439,12 +388,6 @@
     <t>Switch-PT-Empty S3</t>
   </si>
   <si>
-    <t>Switch-PT-Empty S4</t>
-  </si>
-  <si>
-    <t>Switch-PT-Empty S5</t>
-  </si>
-  <si>
     <t>Laptop 6</t>
   </si>
   <si>
@@ -461,6 +404,108 @@
   </si>
   <si>
     <t>192.168.30.66</t>
+  </si>
+  <si>
+    <t>192.168.30.67</t>
+  </si>
+  <si>
+    <t>Switch-PT-Empty S1</t>
+  </si>
+  <si>
+    <t>Switch-PT-Empty S2</t>
+  </si>
+  <si>
+    <t>192.168.30.68</t>
+  </si>
+  <si>
+    <t>192.168.30.69</t>
+  </si>
+  <si>
+    <t>192.168.30.70</t>
+  </si>
+  <si>
+    <t>192.168.30.71</t>
+  </si>
+  <si>
+    <t>EtherChannel LACP</t>
+  </si>
+  <si>
+    <t>Rendszergazda konzol kábeles laptop</t>
+  </si>
+  <si>
+    <t>Internetszolgáltató</t>
+  </si>
+  <si>
+    <t>REST-API</t>
+  </si>
+  <si>
+    <t>Windows Server</t>
+  </si>
+  <si>
+    <t>Linux Server</t>
+  </si>
+  <si>
+    <t>DNS Server</t>
+  </si>
+  <si>
+    <t>AAA Server</t>
+  </si>
+  <si>
+    <t>fd50:50::2</t>
+  </si>
+  <si>
+    <t>fd50:100::1</t>
+  </si>
+  <si>
+    <t>fd50:100::2</t>
+  </si>
+  <si>
+    <t>fd50:101::1</t>
+  </si>
+  <si>
+    <t>fd50:101::x</t>
+  </si>
+  <si>
+    <t>fd50:30::1</t>
+  </si>
+  <si>
+    <t>fd50:50::10</t>
+  </si>
+  <si>
+    <t>fd50:30::254</t>
+  </si>
+  <si>
+    <t>fd50:50::3</t>
+  </si>
+  <si>
+    <t>fd50:30::2</t>
+  </si>
+  <si>
+    <t>fd50:30::4</t>
+  </si>
+  <si>
+    <t>fd50:30::6</t>
+  </si>
+  <si>
+    <t>fd50:30::7</t>
+  </si>
+  <si>
+    <t>fd50:99::11</t>
+  </si>
+  <si>
+    <t>Irodahelyiség</t>
+  </si>
+  <si>
+    <t>HR</t>
+  </si>
+  <si>
+    <t>WAN</t>
+  </si>
+  <si>
+    <t>Szerver terem</t>
+  </si>
+  <si>
+    <t>Hálózati cím 192.168.20.0 /24</t>
   </si>
 </sst>
 </file>
@@ -504,7 +549,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -583,6 +628,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFA56FC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="4">
     <border>
@@ -637,7 +694,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -657,7 +714,20 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
@@ -666,10 +736,10 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFA56FC"/>
       <color rgb="FF6699FF"/>
       <color rgb="FFFD80FF"/>
       <color rgb="FFF705EB"/>
-      <color rgb="FFFA56FC"/>
       <color rgb="FFBE14D9"/>
     </mruColors>
   </colors>
@@ -994,140 +1064,125 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="24" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="12" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>84</v>
+        <v>7</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>13</v>
+        <v>70</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>116</v>
       </c>
       <c r="E3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>14</v>
+      <c r="G3" s="12" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>16</v>
+        <v>70</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>117</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>19</v>
+        <v>70</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>118</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>22</v>
+        <v>71</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>23</v>
+        <v>72</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>119</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>25</v>
+        <v>109</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>27</v>
+        <v>70</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>120</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>7</v>
@@ -1136,16 +1191,16 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>28</v>
+        <v>110</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>30</v>
+        <v>70</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>121</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>7</v>
@@ -1154,16 +1209,16 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>31</v>
+        <v>107</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>33</v>
+        <v>70</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>122</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>7</v>
@@ -1172,16 +1227,16 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>34</v>
+        <v>108</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>36</v>
+        <v>70</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>123</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>7</v>
@@ -1190,22 +1245,27 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>38</v>
+        <v>70</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>124</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>40</v>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="21" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -1230,225 +1290,230 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>43</v>
+        <v>81</v>
+      </c>
+      <c r="D15" s="26" t="s">
+        <v>26</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="G15" s="13" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>45</v>
+        <v>81</v>
+      </c>
+      <c r="D16" s="26" t="s">
+        <v>28</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>48</v>
+        <v>81</v>
+      </c>
+      <c r="D17" s="26" t="s">
+        <v>31</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>50</v>
+        <v>72</v>
+      </c>
+      <c r="D18" s="26" t="s">
+        <v>33</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>53</v>
+        <v>81</v>
+      </c>
+      <c r="D19" s="26" t="s">
+        <v>36</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>55</v>
+        <v>81</v>
+      </c>
+      <c r="D20" s="26" t="s">
+        <v>38</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>57</v>
+        <v>81</v>
+      </c>
+      <c r="D21" s="26" t="s">
+        <v>40</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>59</v>
+        <v>81</v>
+      </c>
+      <c r="D22" s="26" t="s">
+        <v>42</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D23" s="5" t="s">
-        <v>63</v>
+      <c r="D23" s="26" t="s">
+        <v>46</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>66</v>
+        <v>81</v>
+      </c>
+      <c r="D24" s="26" t="s">
+        <v>49</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>69</v>
+        <v>81</v>
+      </c>
+      <c r="D25" s="26" t="s">
+        <v>52</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>67</v>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="22" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -1473,108 +1538,115 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D29" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="D29" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="E29" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="E29" s="10" t="s">
-        <v>10</v>
-      </c>
       <c r="F29" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="G29" s="19"/>
+        <v>54</v>
+      </c>
+      <c r="G29" s="25" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="C30" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D30" s="10" t="s">
-        <v>13</v>
+      <c r="D30" s="19" t="s">
+        <v>112</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F30" s="10" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="C31" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D31" s="10" t="s">
-        <v>16</v>
+      <c r="D31" s="19" t="s">
+        <v>113</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="F31" s="10" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="C32" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D32" s="10" t="s">
-        <v>19</v>
+      <c r="D32" s="19" t="s">
+        <v>114</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F32" s="10" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="11" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="C33" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D33" s="10" t="s">
-        <v>23</v>
+      <c r="D33" s="19" t="s">
+        <v>115</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="F33" s="10" t="s">
-        <v>83</v>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="23" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="14" t="s">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="B36" s="15" t="s">
         <v>1</v>
@@ -1583,7 +1655,7 @@
         <v>2</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="E36" s="15" t="s">
         <v>4</v>
@@ -1594,78 +1666,119 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="16" t="s">
-        <v>106</v>
-      </c>
-      <c r="B37" s="17"/>
-      <c r="C37" s="17"/>
+        <v>97</v>
+      </c>
+      <c r="B37" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="C37" s="17" t="s">
+        <v>70</v>
+      </c>
       <c r="D37" s="17"/>
-      <c r="E37" s="17"/>
-      <c r="F37" s="17"/>
+      <c r="E37" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="F37" s="17" t="s">
+        <v>103</v>
+      </c>
       <c r="G37" s="18" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="16" t="s">
-        <v>107</v>
-      </c>
-      <c r="B38" s="17"/>
-      <c r="C38" s="17"/>
+        <v>98</v>
+      </c>
+      <c r="B38" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="C38" s="17" t="s">
+        <v>70</v>
+      </c>
       <c r="D38" s="17"/>
-      <c r="E38" s="17"/>
-      <c r="F38" s="17"/>
+      <c r="E38" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="F38" s="17" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="B39" s="17"/>
-      <c r="C39" s="17"/>
+        <v>89</v>
+      </c>
+      <c r="B39" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="C39" s="17" t="s">
+        <v>70</v>
+      </c>
       <c r="D39" s="17"/>
-      <c r="E39" s="17"/>
-      <c r="F39" s="17"/>
+      <c r="E39" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="F39" s="17" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="16" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="B40" s="17" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="C40" s="17" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="D40" s="17"/>
-      <c r="E40" s="17"/>
-      <c r="F40" s="17"/>
+      <c r="E40" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="F40" s="17" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="B41" s="17"/>
-      <c r="C41" s="17"/>
+        <v>91</v>
+      </c>
+      <c r="B41" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="C41" s="17" t="s">
+        <v>70</v>
+      </c>
       <c r="D41" s="17"/>
-      <c r="E41" s="17"/>
-      <c r="F41" s="17"/>
+      <c r="E41" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="F41" s="17" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="16" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="B42" s="17" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="C42" s="17" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="D42" s="17"/>
-      <c r="E42" s="17"/>
-      <c r="F42" s="17"/>
+      <c r="E42" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="F42" s="17" t="s">
+        <v>106</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/Packet Tracer/VLSM.xlsx
+++ b/Packet Tracer/VLSM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Vizsgaremek\Packet Tracer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B11DA2A-3251-4C28-A82E-89AEF109565E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA72CBDD-27E4-43BE-BE3E-5638F3F0E1F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{282A7FAF-A36E-4327-A1FC-20DFE78AAB8B}"/>
+    <workbookView xWindow="11670" yWindow="4665" windowWidth="18000" windowHeight="9270" xr2:uid="{282A7FAF-A36E-4327-A1FC-20DFE78AAB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="132">
   <si>
     <t>Eszköz / Interfész</t>
   </si>
@@ -506,6 +506,12 @@
   </si>
   <si>
     <t>Hálózati cím 192.168.20.0 /24</t>
+  </si>
+  <si>
+    <t>200.100.0.10</t>
+  </si>
+  <si>
+    <t>200.100.0.1</t>
   </si>
 </sst>
 </file>
@@ -1744,14 +1750,14 @@
         <v>91</v>
       </c>
       <c r="B41" s="17" t="s">
-        <v>99</v>
+        <v>130</v>
       </c>
       <c r="C41" s="17" t="s">
         <v>70</v>
       </c>
       <c r="D41" s="17"/>
       <c r="E41" s="17" t="s">
-        <v>100</v>
+        <v>131</v>
       </c>
       <c r="F41" s="17" t="s">
         <v>105</v>
@@ -1783,15 +1789,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokumentum" ma:contentTypeID="0x01010023F5B51375CA5F48927837B7C846372A" ma:contentTypeVersion="9" ma:contentTypeDescription="Új dokumentum létrehozása." ma:contentTypeScope="" ma:versionID="8569a69c5601f6c1bb879d16883b0958">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="5d86d87e-4eda-498c-af70-6f2a616ddbb6" xmlns:ns4="04042892-774f-4e1e-9f29-f5d0072c223e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a67e81d8575ab49cd545615425cd976b" ns3:_="" ns4:_="">
     <xsd:import namespace="5d86d87e-4eda-498c-af70-6f2a616ddbb6"/>
@@ -1986,6 +1983,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1995,14 +2001,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4803927-6207-4FE4-B061-1837ED41B397}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{892E8834-8248-4024-B715-C322DC7266E8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2017,6 +2015,14 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4803927-6207-4FE4-B061-1837ED41B397}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
